--- a/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_nearest_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_nearest_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>7.126087697599305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03059659378960385</v>
+        <v>-0.04454190956602597</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03065446603083951</v>
+        <v>0.04459978180726162</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>7.131018938021787</v>
       </c>
       <c r="I3" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03063054855590915</v>
+        <v>-0.04457586433233127</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03062051126453421</v>
+        <v>0.04456582704095632</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>7.119546091650808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03059882368495578</v>
+        <v>-0.04454413946137789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03065223613548759</v>
+        <v>0.0445975519119097</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>7.100810110970246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.03061302679329677</v>
+        <v>-0.04455834256971888</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03063803302714659</v>
+        <v>0.04458334880356871</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>7.067168878436031</v>
       </c>
       <c r="I6" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.03060782161255878</v>
+        <v>-0.0445531373889809</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03064323820788458</v>
+        <v>0.04458855398430669</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>7.032863274890606</v>
       </c>
       <c r="I7" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03060540448493362</v>
+        <v>-0.04455072026135573</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03064565533550975</v>
+        <v>0.04459097111193186</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>6.993709338701228</v>
       </c>
       <c r="I8" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03061370023647355</v>
+        <v>-0.04455901601289566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03063735958396981</v>
+        <v>0.04458267536039193</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>6.983724528837069</v>
       </c>
       <c r="I9" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.03060397224432661</v>
+        <v>-0.04454928802074873</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03064708757611675</v>
+        <v>0.04459240335253886</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6.960628141174349</v>
       </c>
       <c r="I10" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.03060322603401618</v>
+        <v>-0.0445485418104383</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03064783378642718</v>
+        <v>0.04459314956284929</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6.94783602095504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.03062419376213795</v>
+        <v>-0.04456950953856006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03062686605830541</v>
+        <v>0.04457218183472753</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>6.922126041201317</v>
       </c>
       <c r="I12" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.03059650922105436</v>
+        <v>-0.04454182499747647</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03065455059938901</v>
+        <v>0.04459986637581112</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6.89075156037469</v>
       </c>
       <c r="I13" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.03061413140337751</v>
+        <v>-0.04455944717979962</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03063692841706585</v>
+        <v>0.04458224419348797</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6.900103308668752</v>
       </c>
       <c r="I14" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.03060321644878935</v>
+        <v>-0.04454853222521146</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03064784337165401</v>
+        <v>0.04459315914807613</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>6.885252288781944</v>
       </c>
       <c r="I15" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.03061159571816548</v>
+        <v>-0.0445569114945876</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03063946410227788</v>
+        <v>0.04458477987869999</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>6.87573475618544</v>
       </c>
       <c r="I16" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03060081764192154</v>
+        <v>-0.04454613341834365</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03065024217852182</v>
+        <v>0.04459555795494394</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>6.844228900034523</v>
       </c>
       <c r="I17" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.03061576634522341</v>
+        <v>-0.04456108212164553</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03063529347521995</v>
+        <v>0.04458060925164206</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>6.815347014069063</v>
       </c>
       <c r="I18" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.03060552985486761</v>
+        <v>-0.04455084563128972</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03064552996557576</v>
+        <v>0.04459084574199787</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>6.796059343037657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.03061406943851227</v>
+        <v>-0.04455938521493438</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03063699038193109</v>
+        <v>0.04458230615835321</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>6.817135745764311</v>
       </c>
       <c r="I20" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.03058709998180261</v>
+        <v>-0.04453241575822472</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03066395983864075</v>
+        <v>0.04460927561506287</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>6.83849912124536</v>
       </c>
       <c r="I21" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.03062552991022168</v>
+        <v>-0.0445708456866438</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03062552991022168</v>
+        <v>0.0445708456866438</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>6.825366919713312</v>
       </c>
       <c r="I22" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.02156392011451266</v>
+        <v>-0.03550923589093477</v>
       </c>
       <c r="K22" t="n">
-        <v>0.03968713970593071</v>
+        <v>0.05363245548235282</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>6.815897339622838</v>
       </c>
       <c r="I23" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.01052858402460684</v>
+        <v>-0.02447389980102896</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05072247579583652</v>
+        <v>0.06466779157225863</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>6.806014470275789</v>
       </c>
       <c r="I24" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.007445956448809264</v>
+        <v>-0.02139127222523138</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0538051033716341</v>
+        <v>0.06775041914805621</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>6.78909662269687</v>
       </c>
       <c r="I25" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0003837418993452371</v>
+        <v>-0.01356157387707688</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0616348017197886</v>
+        <v>0.07558011749621071</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>6.825757032673978</v>
       </c>
       <c r="I26" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01289995674312613</v>
+        <v>-0.02684527251954824</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04835110307731724</v>
+        <v>0.06229641885373935</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>6.818453318357642</v>
       </c>
       <c r="I27" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.003197648741288882</v>
+        <v>-0.017142964517711</v>
       </c>
       <c r="K27" t="n">
-        <v>0.05805341107915448</v>
+        <v>0.07199872685557659</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>6.789309752638157</v>
       </c>
       <c r="I28" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01642272663963277</v>
+        <v>0.002477410863210655</v>
       </c>
       <c r="K28" t="n">
-        <v>0.07767378646007614</v>
+        <v>0.09161910223649825</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>6.757856160230959</v>
       </c>
       <c r="I29" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0250473411509912</v>
+        <v>0.01110202537456909</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08629840097143457</v>
+        <v>0.1002437167478567</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>6.750049924385731</v>
       </c>
       <c r="I30" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J30" t="n">
-        <v>0.02024542389527665</v>
+        <v>0.006300108118854536</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08149648371572002</v>
+        <v>0.09544179949214213</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>6.744828592376146</v>
       </c>
       <c r="I31" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02315078452282685</v>
+        <v>0.009205468746404738</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08440184434327022</v>
+        <v>0.09834716011969233</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>6.756580126087248</v>
       </c>
       <c r="I32" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0273483528867459</v>
+        <v>0.01340303711032378</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08859941270718927</v>
+        <v>0.1025447284836114</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>6.768440331274862</v>
       </c>
       <c r="I33" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03335508459302387</v>
+        <v>0.01940976881660175</v>
       </c>
       <c r="K33" t="n">
-        <v>0.09460614441346724</v>
+        <v>0.1085514601898893</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>6.764660560599898</v>
       </c>
       <c r="I34" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04156870356421419</v>
+        <v>0.02762338778779208</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1028197633846576</v>
+        <v>0.1167650791610797</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>6.77587543287222</v>
       </c>
       <c r="I35" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03993198701379478</v>
+        <v>0.02598667123737267</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1011830468342381</v>
+        <v>0.1151283626106603</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>6.763753229052751</v>
       </c>
       <c r="I36" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04496789441364638</v>
+        <v>0.03102257863722427</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1062189542340898</v>
+        <v>0.1201642700105119</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>6.753318646496826</v>
       </c>
       <c r="I37" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J37" t="n">
-        <v>0.04532925511553946</v>
+        <v>0.03138393933911734</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1065803149359828</v>
+        <v>0.1205256307124049</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>6.773870540945235</v>
       </c>
       <c r="I38" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J38" t="n">
-        <v>0.03743919247673003</v>
+        <v>0.02349387670030792</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0986902522971734</v>
+        <v>0.1126355680735955</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>6.764890726551868</v>
       </c>
       <c r="I39" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04155855317501748</v>
+        <v>0.02761323739859536</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1028096129954608</v>
+        <v>0.116754928771883</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>6.760049415700732</v>
       </c>
       <c r="I40" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04309369245479414</v>
+        <v>0.02914837667837203</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1043447522752375</v>
+        <v>0.1182900680516596</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>6.729892817568365</v>
       </c>
       <c r="I41" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J41" t="n">
-        <v>0.05274603028520312</v>
+        <v>0.038800714508781</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1139970901056465</v>
+        <v>0.1279424058820686</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>6.709372479113942</v>
       </c>
       <c r="I42" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J42" t="n">
-        <v>0.05133610061889585</v>
+        <v>0.03739078484247374</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1125871604393392</v>
+        <v>0.1265324762157613</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>6.691514997318452</v>
       </c>
       <c r="I43" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J43" t="n">
-        <v>0.05206215060438205</v>
+        <v>0.03811683482795994</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1133132104248254</v>
+        <v>0.1272585262012475</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>6.70881831354767</v>
       </c>
       <c r="I44" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J44" t="n">
-        <v>0.05167529539459929</v>
+        <v>0.03772997961817717</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1129263552150427</v>
+        <v>0.1268716709914648</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>6.73332992482224</v>
       </c>
       <c r="I45" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J45" t="n">
-        <v>0.05143812866316236</v>
+        <v>0.03749281288674025</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1126891884836057</v>
+        <v>0.1266345042600278</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>6.726465349444537</v>
       </c>
       <c r="I46" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05413365017115482</v>
+        <v>0.04018833439473271</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1153847099915982</v>
+        <v>0.1293300257680203</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>6.733490353554068</v>
       </c>
       <c r="I47" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05643607106999441</v>
+        <v>0.0424907552935723</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1176871308904378</v>
+        <v>0.1316324466668599</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>6.721287493017218</v>
       </c>
       <c r="I48" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J48" t="n">
-        <v>0.06842870807807824</v>
+        <v>0.05448339230165614</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1296797678985216</v>
+        <v>0.1436250836749437</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>6.720820791276677</v>
       </c>
       <c r="I49" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06282409690991778</v>
+        <v>0.04887878113349567</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1240751567303612</v>
+        <v>0.1380204725067833</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>6.736368427801649</v>
       </c>
       <c r="I50" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J50" t="n">
-        <v>0.06021087701614417</v>
+        <v>0.04626556123972206</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1214619368365875</v>
+        <v>0.1354072526130096</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>6.723919842003034</v>
       </c>
       <c r="I51" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0780104430650658</v>
+        <v>0.06406512728864369</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1392615028855092</v>
+        <v>0.1532068186619313</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>6.715321061458185</v>
       </c>
       <c r="I52" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0804257696771126</v>
+        <v>0.06648045390069049</v>
       </c>
       <c r="K52" t="n">
-        <v>0.141676829497556</v>
+        <v>0.1556221452739781</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>6.679552656350155</v>
       </c>
       <c r="I53" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J53" t="n">
-        <v>0.08802351842084236</v>
+        <v>0.07407820264442025</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1492745782412857</v>
+        <v>0.1632198940177078</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>6.662972191103021</v>
       </c>
       <c r="I54" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J54" t="n">
-        <v>0.09024593467445677</v>
+        <v>0.07630061889803466</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1514969944949001</v>
+        <v>0.1654423102713223</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>6.645697589772843</v>
       </c>
       <c r="I55" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J55" t="n">
-        <v>0.09364423412189141</v>
+        <v>0.0796989183454693</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1548952939423348</v>
+        <v>0.1688406097187569</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>6.669171371326142</v>
       </c>
       <c r="I56" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J56" t="n">
-        <v>0.09371043513031854</v>
+        <v>0.07976511935389644</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1549614949507619</v>
+        <v>0.168906810727184</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>6.687991230589503</v>
       </c>
       <c r="I57" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0952945943911713</v>
+        <v>0.08134927861474919</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1565456542116147</v>
+        <v>0.1704909699880368</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>6.674440913556873</v>
       </c>
       <c r="I58" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1084781008202821</v>
+        <v>0.09453278504386001</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1697291606407255</v>
+        <v>0.1836744764171476</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>6.680698456100704</v>
       </c>
       <c r="I59" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1077570169985108</v>
+        <v>0.09381170122208873</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1690080768189542</v>
+        <v>0.1829533925953763</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>6.67078687616881</v>
       </c>
       <c r="I60" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1163318712980303</v>
+        <v>0.1023865555216082</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1775829311184736</v>
+        <v>0.1915282468948958</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>6.673889773862733</v>
       </c>
       <c r="I61" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1044637482703172</v>
+        <v>0.09051843249389505</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1657148080907605</v>
+        <v>0.1796601238671826</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>6.673389384606637</v>
       </c>
       <c r="I62" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1159327313415929</v>
+        <v>0.1019874155651708</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1771837911620363</v>
+        <v>0.1911291069384584</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>6.676303545367765</v>
       </c>
       <c r="I63" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1163895031864483</v>
+        <v>0.1024441874100262</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1776405630068917</v>
+        <v>0.1915858787833138</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>6.666547269040468</v>
       </c>
       <c r="I64" t="n">
-        <v>0.015625270362358</v>
+        <v>0.0227402273911448</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1317376196674397</v>
+        <v>0.1177923038910176</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1929886794878831</v>
+        <v>0.2069339952643052</v>
       </c>
     </row>
   </sheetData>
